--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487466_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487466_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2483</v>
+        <v>6.3124</v>
       </c>
       <c r="E2" t="n">
-        <v>4.565</v>
+        <v>5.2549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6832</v>
+        <v>1.0574</v>
       </c>
       <c r="G2" t="n">
         <v>5.7533</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6802</v>
+        <v>-0.6161</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.111</v>
+        <v>-0.4211</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5692</v>
+        <v>-0.195</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.739</v>
+        <v>2.687</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0114</v>
+        <v>2.8031</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2724</v>
+        <v>-0.1161</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7922</v>
+        <v>-0.7627</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7243000000000001</v>
+        <v>1.3141</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5165</v>
+        <v>-2.0767</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4578</v>
+        <v>2.207</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2246</v>
+        <v>4.168</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2332</v>
+        <v>-1.9611</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6656</v>
+        <v>-2.9696</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9489</v>
+        <v>-2.854</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2833</v>
+        <v>-0.1157</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>2.546</v>
+        <v>3.7211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4803</v>
+        <v>-0.3752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.217</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0526</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1003</v>
+        <v>3.0415</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.3169</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1003</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0949</v>
+        <v>2.4589</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3179</v>
+        <v>2.6779</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.223</v>
+        <v>-0.219</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7627</v>
+        <v>2.7922</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3141</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0767</v>
+        <v>3.5165</v>
       </c>
       <c r="J4" t="n">
-        <v>2.207</v>
+        <v>3.4578</v>
       </c>
       <c r="K4" t="n">
-        <v>4.168</v>
+        <v>0.2246</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9611</v>
+        <v>3.2332</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9696</v>
+        <v>-0.6656</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.854</v>
+        <v>-0.9489</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1157</v>
+        <v>0.2833</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7211</v>
+        <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9674</v>
+        <v>0.2003</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2682</v>
+        <v>0.1994</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6992</v>
+        <v>0.0009</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0415</v>
+        <v>-2.1003</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3169</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0605</v>
+        <v>2.3826</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6791</v>
+        <v>1.8408</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3814</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.7691</v>
@@ -844,13 +844,13 @@
         <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7247</v>
+        <v>-0.4026</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6952</v>
+        <v>-0.5334</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0295</v>
+        <v>0.1309</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5507</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5788</v>
+        <v>1.1486</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7733</v>
+        <v>1.4234</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1946</v>
+        <v>-0.2748</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3216</v>
@@ -922,13 +922,13 @@
         <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1953</v>
+        <v>-0.2348</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0723</v>
+        <v>-0.4223</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2677</v>
+        <v>0.1875</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0576</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7389</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7885</v>
+        <v>0.7456</v>
       </c>
       <c r="F7" t="n">
         <v>-1.5274</v>
@@ -1000,10 +1000,10 @@
         <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3564</v>
+        <v>-0.3993</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0047</v>
+        <v>-0.0382</v>
       </c>
       <c r="U7" t="n">
         <v>-0.3611</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2155</v>
+        <v>-1.1353</v>
       </c>
       <c r="E8" t="n">
         <v>-0.6284999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.587</v>
+        <v>-0.5068</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8179</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2018</v>
+        <v>-0.1216</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4045</v>
+        <v>-2.3138</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5131</v>
+        <v>-0.556</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8915</v>
+        <v>-1.7578</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8923</v>
@@ -1156,13 +1156,13 @@
         <v>3.1336</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5467</v>
+        <v>-0.456</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1141</v>
+        <v>-0.157</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4326</v>
+        <v>-0.2989</v>
       </c>
       <c r="V9" t="n">
         <v>-3.0991</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7389</v>
+        <v>-3.9082</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7337</v>
+        <v>-2.5555</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0052</v>
+        <v>-1.3527</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8259</v>
@@ -1234,13 +1234,13 @@
         <v>2.3502</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1665</v>
+        <v>-0.0028</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2682</v>
+        <v>-0.09</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4347</v>
+        <v>0.0872</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1696</v>
+        <v>-5.2588</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4531</v>
+        <v>-4.0077</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7165</v>
+        <v>-1.2511</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3855</v>
@@ -1312,13 +1312,13 @@
         <v>2.9377</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9198</v>
+        <v>-0.1694</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4493</v>
+        <v>-0.1053</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4705</v>
+        <v>-0.0641</v>
       </c>
       <c r="V11" t="n">
         <v>0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.962</v>
+        <v>-6.9117</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1777</v>
+        <v>-5.1808</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7844</v>
+        <v>-1.7309</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0979</v>
@@ -1390,13 +1390,13 @@
         <v>3.1336</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5312</v>
+        <v>-0.4808</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9328</v>
+        <v>0.0641</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5984</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5495</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.507899999999999</v>
+        <v>-5.3201</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6290999999999984</v>
+        <v>1.8172</v>
       </c>
       <c r="F13" t="n">
         <v>-7.1374</v>
@@ -1435,7 +1435,7 @@
         <v>-4.1348</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7183</v>
+        <v>-2.718300000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-1.4162</v>
@@ -1447,7 +1447,7 @@
         <v>17.6654</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8898999999999995</v>
+        <v>-0.8899000000000004</v>
       </c>
       <c r="M13" t="n">
         <v>-20.9105</v>
@@ -1468,13 +1468,13 @@
         <v>27.4188</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.246499999999999</v>
+        <v>-3.0583</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.593799999999999</v>
+        <v>-1.4056</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6527</v>
+        <v>-1.6525</v>
       </c>
       <c r="V13" t="n">
         <v>-4.9816</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.167899999999999</v>
+        <v>8.795500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2646</v>
+        <v>6.7529</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9033</v>
+        <v>2.0426</v>
       </c>
       <c r="G14" t="n">
         <v>1.7468</v>
@@ -1546,13 +1546,13 @@
         <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8935</v>
+        <v>1.5211</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1139</v>
+        <v>0.6022</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7796</v>
+        <v>0.9188</v>
       </c>
       <c r="V14" t="n">
         <v>3.765</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0905</v>
+        <v>3.5459</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8812</v>
+        <v>2.9835</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2093</v>
+        <v>0.5624</v>
       </c>
       <c r="G15" t="n">
         <v>5.7922</v>
@@ -1624,13 +1624,13 @@
         <v>4.1128</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7245</v>
+        <v>1.1799</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3129</v>
+        <v>0.4152</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4116</v>
+        <v>0.7647</v>
       </c>
       <c r="V15" t="n">
         <v>1.2742</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. OKEKE</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6919</v>
+        <v>0.3245</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3753</v>
+        <v>1.6211</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0671</v>
+        <v>-1.2966</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8382</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4184</v>
+        <v>0.492</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4197</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8599</v>
+        <v>1.7135</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2036</v>
+        <v>1.1024</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6563</v>
+        <v>0.611</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0218</v>
+        <v>-1.1354</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7852</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2366</v>
+        <v>-0.525</v>
       </c>
       <c r="P16" t="n">
-        <v>-5.0921</v>
+        <v>0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.8132</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.7211</v>
+        <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0621</v>
+        <v>0.122</v>
       </c>
       <c r="T16" t="n">
-        <v>2.419</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6431</v>
+        <v>0.2144</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8837</v>
+        <v>-1.159</v>
       </c>
       <c r="W16" t="n">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>D. PALACIOS AQUINO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.177</v>
+        <v>-0.4042</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4165</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5935</v>
+        <v>-0.4042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5780999999999999</v>
+        <v>-0.4042</v>
       </c>
       <c r="H17" t="n">
-        <v>0.492</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.4042</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7135</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1024</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.611</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1354</v>
+        <v>-0.4042</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.525</v>
+        <v>-0.4042</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3795</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.297</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0825</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. PALACIOS AQUINO</t>
+          <t>I. OKEKE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4042</v>
+        <v>-0.6016</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-1.808</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4042</v>
+        <v>1.2064</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4042</v>
+        <v>1.8382</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.4184</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4042</v>
+        <v>0.4197</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>4.8599</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.2036</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6563</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4042</v>
+        <v>-3.0218</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-2.7852</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4042</v>
+        <v>-0.2366</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-5.0921</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-8.8132</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.7211</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.7687</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.9863</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.7824</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9203</v>
+        <v>-0.6732</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1915</v>
+        <v>-0.5594</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1118</v>
+        <v>-0.1138</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0091</v>
+        <v>-2.0151</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1467</v>
+        <v>-1.7826</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1376</v>
+        <v>-0.2325</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2793</v>
+        <v>1.2046</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1176</v>
+        <v>1.3422</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1617</v>
+        <v>-0.1376</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2884</v>
+        <v>-3.2197</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.2643</v>
+        <v>-3.1248</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9759</v>
+        <v>-0.0949</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1336</v>
+        <v>3.917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4633</v>
+        <v>0.4202</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0129</v>
+        <v>0.0147</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4763</v>
+        <v>0.4055</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5495</v>
+        <v>-0.0576</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8837</v>
+        <v>1.159</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4332</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3878</v>
+        <v>-0.8225</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5559</v>
+        <v>0.3962</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1682</v>
+        <v>-1.2187</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3919</v>
+        <v>-1.0091</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.558</v>
+        <v>-2.1467</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8339</v>
+        <v>1.1376</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5753</v>
+        <v>1.2793</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8199</v>
+        <v>1.1176</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3952</v>
+        <v>0.1617</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8166</v>
+        <v>-2.2884</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.3779</v>
+        <v>-3.2643</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5614</v>
+        <v>0.9759</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1543</v>
+        <v>3.1336</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0582</v>
+        <v>0.5611</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7722</v>
+        <v>0.1917</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7141</v>
+        <v>0.3694</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8249</v>
+        <v>-1.5495</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7086</v>
+        <v>0.8837</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8837</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5529</v>
+        <v>-2.2918</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6851</v>
+        <v>-2.2489</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8678</v>
+        <v>-0.0429</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0151</v>
+        <v>-2.3919</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7826</v>
+        <v>-1.558</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2325</v>
+        <v>-0.8339</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2046</v>
+        <v>-0.5753</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3422</v>
+        <v>0.8199</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1376</v>
+        <v>-1.3952</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.2197</v>
+        <v>-1.8166</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.1248</v>
+        <v>-2.3779</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0949</v>
+        <v>0.5614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9792</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R21" t="n">
-        <v>3.917</v>
+        <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4595</v>
+        <v>0.0378</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.111</v>
+        <v>-0.4652</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3485</v>
+        <v>0.503</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0576</v>
+        <v>1.8249</v>
       </c>
       <c r="W21" t="n">
-        <v>1.159</v>
+        <v>2.7086</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.508099999999999</v>
+        <v>7.872599999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>7.137499999999999</v>
+        <v>7.1374</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6294000000000002</v>
+        <v>0.7352000000000005</v>
       </c>
       <c r="G22" t="n">
         <v>4.135</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7184</v>
+        <v>2.718400000000001</v>
       </c>
       <c r="I22" t="n">
         <v>1.4163</v>
@@ -2149,7 +2149,7 @@
         <v>20.3838</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5265000000000002</v>
+        <v>0.5264999999999997</v>
       </c>
       <c r="M22" t="n">
         <v>-16.7755</v>
@@ -2161,7 +2161,7 @@
         <v>0.8897999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-6.8548</v>
+        <v>-6.854800000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-27.4188</v>
@@ -2170,13 +2170,13 @@
         <v>20.5641</v>
       </c>
       <c r="S22" t="n">
-        <v>4.246199999999999</v>
+        <v>5.610799999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6527</v>
+        <v>1.6526</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5937</v>
+        <v>3.9582</v>
       </c>
       <c r="V22" t="n">
         <v>4.9817</v>
@@ -2185,7 +2185,7 @@
         <v>11.9933</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.0117</v>
+        <v>-7.011699999999999</v>
       </c>
     </row>
   </sheetData>
